--- a/jogos_2024-10-24.xlsx
+++ b/jogos_2024-10-24.xlsx
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,80 +1185,80 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="M6" t="n">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['7', '28']</t>
+          <t>['15', '49', '57']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AJ6" t="n">
         <v>2.3</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,80 +1314,80 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
-        <v>3.27</v>
+        <v>3.49</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['15', '49', '57']</t>
+          <t>['7', '28']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AJ7" t="n">
         <v>2.3</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.83</v>
+        <v>2.32</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>3.34</v>
       </c>
       <c r="N8" t="n">
-        <v>1.39</v>
+        <v>2.99</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X8" t="n">
         <v>3.45</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['55', '59', '72']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.57</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AI8" t="n">
-        <v>2.85</v>
+        <v>1.91</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45589.625</v>
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.32</v>
+        <v>5.83</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>4.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>1.39</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.45</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['55', '59', '72']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.91</v>
+        <v>2.85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45589.625</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>3.04</v>
+        <v>3.47</v>
       </c>
       <c r="N12" t="n">
-        <v>4.42</v>
+        <v>3.94</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG12" t="n">
         <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45589.66666666666</v>
@@ -2062,16 +2062,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -2080,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,80 +2088,80 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.94</v>
+        <v>4.71</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="X13" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['5', '79']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ13" t="n">
         <v>2.88</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,55 +2217,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="M14" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="N14" t="n">
-        <v>4.71</v>
+        <v>4.42</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="X14" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
         <v>2.15</v>
@@ -2275,25 +2275,25 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['5', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45589.66666666666</v>
